--- a/data/INPUT/linhkien1.xlsx
+++ b/data/INPUT/linhkien1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\electronic_library\data\INPUT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B19B3B85-30D3-4FA5-99F6-9B1F1282C3D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BDFCBEB-A980-43D1-A1AC-A759841F3EEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{C8D6545E-1ABA-4D8D-85FD-F9EC3B1B119D}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6726" uniqueCount="2415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6722" uniqueCount="2415">
   <si>
     <t>Tên Linh Kiện</t>
   </si>
@@ -8126,7 +8126,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F49D843D-7FD4-4067-A002-C3CFE2844386}">
-  <dimension ref="A1:J1180"/>
+  <dimension ref="A1:J1179"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="45.1796875" customWidth="1"/>
@@ -35695,23 +35695,6 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="1180" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1180" t="s">
-        <v>2153</v>
-      </c>
-      <c r="B1180" t="s">
-        <v>2334</v>
-      </c>
-      <c r="C1180">
-        <v>0</v>
-      </c>
-      <c r="D1180" t="s">
-        <v>2406</v>
-      </c>
-      <c r="E1180" t="s">
-        <v>2414</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
